--- a/artfynd/A 2954-2023 artfynd.xlsx
+++ b/artfynd/A 2954-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746042</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956925</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969451</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970048</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970893</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,8 +1504,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971323</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 2954-2023 artfynd.xlsx
+++ b/artfynd/A 2954-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134960888</v>
       </c>
       <c r="B2" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>134956925</v>
       </c>
       <c r="B4" t="n">
-        <v>106494</v>
+        <v>106549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>134962688</v>
       </c>
       <c r="B5" t="n">
-        <v>106494</v>
+        <v>106549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>134969451</v>
       </c>
       <c r="B6" t="n">
-        <v>106494</v>
+        <v>106549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>134970048</v>
       </c>
       <c r="B7" t="n">
-        <v>106494</v>
+        <v>106549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>134970893</v>
       </c>
       <c r="B8" t="n">
-        <v>106494</v>
+        <v>106549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>134971323</v>
       </c>
       <c r="B9" t="n">
-        <v>106494</v>
+        <v>106549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
